--- a/jogos_2025-06-05.xlsx
+++ b/jogos_2025-06-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -127,91 +127,25 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
     <t>18:00</t>
   </si>
   <si>
-    <t>20:00</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
     <t>Coritiba</t>
   </si>
   <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>incomplete</t>
+    <t>complete</t>
   </si>
   <si>
     <t>[]</t>
@@ -578,10 +512,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,79 +630,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45813</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -783,16 +663,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L2">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N2">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="O2">
         <v>2.2</v>
@@ -804,291 +684,67 @@
         <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="T2">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V2">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y2">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Z2">
         <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB2">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="AC2">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AD2">
-        <v>5.75</v>
+        <v>4.3</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG2">
         <v>1.65</v>
       </c>
       <c r="AH2">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="AI2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL2">
-        <v>1.4</v>
-      </c>
-      <c r="AM2">
-        <v>1.35</v>
-      </c>
-      <c r="AN2">
-        <v>1.44</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>1.2</v>
-      </c>
-      <c r="AQ2">
-        <v>1.27</v>
-      </c>
-      <c r="AR2">
-        <v>1.83</v>
-      </c>
-      <c r="AS2">
-        <v>2.03</v>
-      </c>
-      <c r="AT2">
-        <v>2.54</v>
-      </c>
-      <c r="AU2">
-        <v>3.88</v>
-      </c>
-      <c r="AV2">
-        <v>2.77</v>
-      </c>
-      <c r="AW2">
-        <v>2.16</v>
-      </c>
-      <c r="AX2">
-        <v>1.75</v>
-      </c>
-      <c r="AY2">
-        <v>1.43</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2.2</v>
-      </c>
-      <c r="BC2">
-        <v>2.1</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>44</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45813.75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:56">
-      <c r="A3" s="2">
-        <v>45813</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3">
-        <v>2.03</v>
-      </c>
-      <c r="M3">
-        <v>2.8</v>
-      </c>
-      <c r="N3">
-        <v>3.7</v>
-      </c>
-      <c r="O3">
-        <v>1.67</v>
-      </c>
-      <c r="P3">
-        <v>7</v>
-      </c>
-      <c r="Q3">
-        <v>2.88</v>
-      </c>
-      <c r="R3">
-        <v>1.69</v>
-      </c>
-      <c r="S3">
-        <v>2.09</v>
-      </c>
-      <c r="T3">
-        <v>4.4</v>
-      </c>
-      <c r="U3">
-        <v>1.15</v>
-      </c>
-      <c r="V3">
-        <v>11</v>
-      </c>
-      <c r="W3">
-        <v>1.03</v>
-      </c>
-      <c r="X3">
-        <v>1.11</v>
-      </c>
-      <c r="Y3">
-        <v>4.75</v>
-      </c>
-      <c r="Z3">
-        <v>1.71</v>
-      </c>
-      <c r="AA3">
-        <v>2.1</v>
-      </c>
-      <c r="AB3">
-        <v>3.19</v>
-      </c>
-      <c r="AC3">
-        <v>1.36</v>
-      </c>
-      <c r="AD3">
-        <v>6</v>
-      </c>
-      <c r="AE3">
-        <v>1.1</v>
-      </c>
-      <c r="AF3">
-        <v>2.5</v>
-      </c>
-      <c r="AG3">
-        <v>1.5</v>
-      </c>
-      <c r="AH3">
-        <v>12</v>
-      </c>
-      <c r="AI3">
-        <v>1.02</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL3">
-        <v>1.13</v>
-      </c>
-      <c r="AM3">
-        <v>1.31</v>
-      </c>
-      <c r="AN3">
-        <v>1.73</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.45</v>
-      </c>
-      <c r="AQ3">
-        <v>1.75</v>
-      </c>
-      <c r="AR3">
-        <v>2.18</v>
-      </c>
-      <c r="AS3">
-        <v>2.9</v>
-      </c>
-      <c r="AT3">
-        <v>3.9</v>
-      </c>
-      <c r="AU3">
-        <v>2.7</v>
-      </c>
-      <c r="AV3">
-        <v>1.95</v>
-      </c>
-      <c r="AW3">
-        <v>1.58</v>
-      </c>
-      <c r="AX3">
-        <v>1.35</v>
-      </c>
-      <c r="AY3">
-        <v>1.21</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.67</v>
-      </c>
-      <c r="BC3">
-        <v>2.88</v>
-      </c>
-      <c r="BD3" s="3">
-        <v>45813.83333333334</v>
       </c>
     </row>
   </sheetData>
